--- a/data/Noi dung SICK/00 CAN SOAT DICH.xlsx
+++ b/data/Noi dung SICK/00 CAN SOAT DICH.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>HF transponders</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -494,19 +494,19 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>W12-2 Laser; W12 Teflon; W12-3; W12; W12-2 AS-i; W12G</t>
+          <t>NXP ICODE SLIX2; Fujitsu MB89R118; Texas Instruments Tag-it HF-I; NXP ICODE SLIX</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>W12-2 Laser; W12 Teflon; W12-3; W12; W12-2 AS-i; W12G</t>
+          <t>NXP ICODE SLIX2; Fujitsu MB89R118; Texas Instruments Tag-it HF-I; NXP ICODE SLIX</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MLG-2</t>
+          <t>UHF transponders</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -521,12 +521,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>RS-485 + 6 x Q + 2 x I/O; 2 x analog + 1 x Q (IO-Link); 3 x Q (IO-Link); RS-485 + 2 x Q (IO-Link); 2 x analog + 2 x Q (IO-Link); 4 x Q (IO-Link)</t>
+          <t>NXP UCODE G2iM; Impinj Monza 4E; NXP UCODE 9xm; Impinj Monza 4QT; Impinj Monza X 8k; NXP UCODE G2XM (+9 tuỳ chọn khác)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>RS-485 + 6 x Q + 2 x I/O; 2 x analog + 1 x Q (IO-Link); 3 x Q (IO-Link); RS-485 + 2 x Q (IO-Link); 2 x analog + 2 x Q (IO-Link); 4 x Q (IO-Link)</t>
+          <t>NXP UCODE G2iM; Impinj Monza 4E; NXP UCODE 9xm; Impinj Monza 4QT; Impinj Monza X 8k; NXP UCODE G2XM (+9 tuỳ chọn khác)</t>
         </is>
       </c>
     </row>
@@ -548,19 +548,19 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>MLGxxNxxxxHxxxxx; MLGxxS-xxxxAx; MLGxxS-xxxxDx; MLGxxN-xxxxNx; MLGxxA-xxxxRx; MLGxxA-xxxxIx (+3 tuỳ chọn khác)</t>
+          <t>2 x analog + 2 x Q (IO-Link); RS-485 + 2 x Q (IO-Link); 4 x Q (IO-Link); RS-485 + 6 x Q + 2 x I/O; 2 x analog + 1 x Q (IO-Link); 3 x Q (IO-Link)</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>MLGxxNxxxxHxxxxx; MLGxxS-xxxxAx; MLGxxS-xxxxDx; MLGxxN-xxxxNx; MLGxxA-xxxxRx; MLGxxA-xxxxIx (+3 tuỳ chọn khác)</t>
+          <t>2 x analog + 2 x Q (IO-Link); RS-485 + 2 x Q (IO-Link); 4 x Q (IO-Link); RS-485 + 6 x Q + 2 x I/O; 2 x analog + 1 x Q (IO-Link); 3 x Q (IO-Link)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MLG-2 WebChecker</t>
+          <t>MLG-2</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -575,19 +575,19 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>1 x analog + 3 x Q (IO-Link); 2 x analog + 2 x Q (IO-Link); RS-485 + 2 x Q (IO-Link); 4 x Q (IO-Link)</t>
+          <t>MLGxxNxxxxHxxxxx; MLGxxS-xxxxAx; MLGxxN-xxxxEx; MLGxxA-xxxxBx; MLGxxA-xxxxRx; MLGxxA-xxxxIx (+3 tuỳ chọn khác)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1 x analog + 3 x Q (IO-Link); 2 x analog + 2 x Q (IO-Link); RS-485 + 2 x Q (IO-Link); 4 x Q (IO-Link)</t>
+          <t>MLGxxNxxxxHxxxxx; MLGxxS-xxxxAx; MLGxxN-xxxxEx; MLGxxA-xxxxBx; MLGxxA-xxxxRx; MLGxxA-xxxxIx (+3 tuỳ chọn khác)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Sensor-actuator cables</t>
+          <t>MLG-2 WebChecker</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -602,24 +602,24 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>M8; D-Sub; M26; RJ45; D-Sub-HD; M12 (+1 tuỳ chọn khác)</t>
+          <t>4 x Q (IO-Link); 1 x analog + 3 x Q (IO-Link); RS-485 + 2 x Q (IO-Link); 2 x analog + 2 x Q (IO-Link)</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>M8; D-Sub; M26; RJ45; D-Sub-HD; M12 (+1 tuỳ chọn khác)</t>
+          <t>4 x Q (IO-Link); 1 x analog + 3 x Q (IO-Link); RS-485 + 2 x Q (IO-Link); 2 x analog + 2 x Q (IO-Link)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Industrial Ethernet cables and fieldbus cables</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Mô tả ngắn</t>
+          <t>Giá trị thông số</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -629,24 +629,24 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>PROFIBUS, CANopen, Interbus, PROFINET, EtherNet/IP™ &amp; Gigabit Ethernet</t>
+          <t>W12-3; W12-2 AS-i; W12 Teflon; W12; W12-2 Laser; W12G</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>PROFIBUS, CANopen, Interbus, PROFINET, EtherNet/IP™ &amp; Gigabit Ethernet</t>
+          <t>W12-3; W12-2 AS-i; W12 Teflon; W12; W12-2 Laser; W12G</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>HF transponders</t>
+          <t>Industrial Ethernet cables and fieldbus cables</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Giá trị thông số</t>
+          <t>Mô tả ngắn</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -656,39 +656,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Texas Instruments Tag-it HF-I; Fujitsu MB89R118; NXP ICODE SLIX2; NXP ICODE SLIX</t>
+          <t>PROFIBUS, CANopen, Interbus, PROFINET, EtherNet/IP™ &amp; Gigabit Ethernet</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Texas Instruments Tag-it HF-I; Fujitsu MB89R118; NXP ICODE SLIX2; NXP ICODE SLIX</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>HF transponders</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Giá trị thông số</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>chua dich</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Texas Instruments Tag-it HF-I; Fujitsu MB89R118; NXP ICODE SLIX2; NXP ICODE SLIX</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>Texas Instruments Tag-it HF-I; Fujitsu MB89R118; NXP ICODE SLIX2; NXP ICODE SLIX</t>
+          <t>PROFIBUS, CANopen, Interbus, PROFINET, EtherNet/IP™ &amp; Gigabit Ethernet</t>
         </is>
       </c>
     </row>

--- a/data/Noi dung SICK/00 CAN SOAT DICH.xlsx
+++ b/data/Noi dung SICK/00 CAN SOAT DICH.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>HF transponders</t>
+          <t>FlexChain</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -494,19 +494,19 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>NXP ICODE SLIX2; Fujitsu MB89R118; Texas Instruments Tag-it HF-I; NXP ICODE SLIX</t>
+          <t>IO-Link (V1.1); Serial (RS-485); CANopen; IO-Link; Serial</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>NXP ICODE SLIX2; Fujitsu MB89R118; Texas Instruments Tag-it HF-I; NXP ICODE SLIX</t>
+          <t>IO-Link (V1.1); Serial (RS-485); CANopen; IO-Link; Serial</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>UHF transponders</t>
+          <t>Visionary-B Two</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -521,19 +521,19 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>NXP UCODE G2iM; Impinj Monza 4E; NXP UCODE 9xm; Impinj Monza 4QT; Impinj Monza X 8k; NXP UCODE G2XM (+9 tuỳ chọn khác)</t>
+          <t>SICK AppStudio, SICK AppManager, SOPASair</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>NXP UCODE G2iM; Impinj Monza 4E; NXP UCODE 9xm; Impinj Monza 4QT; Impinj Monza X 8k; NXP UCODE G2XM (+9 tuỳ chọn khác)</t>
+          <t>SICK AppStudio, SICK AppManager, SOPASair</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MLG-2</t>
+          <t>DFS2x</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -548,24 +548,24 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>2 x analog + 2 x Q (IO-Link); RS-485 + 2 x Q (IO-Link); 4 x Q (IO-Link); RS-485 + 6 x Q + 2 x I/O; 2 x analog + 1 x Q (IO-Link); 3 x Q (IO-Link)</t>
+          <t>TTL / RS-422; HTL / Push pull; Open Collector; TTL / HTL</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2 x analog + 2 x Q (IO-Link); RS-485 + 2 x Q (IO-Link); 4 x Q (IO-Link); RS-485 + 6 x Q + 2 x I/O; 2 x analog + 1 x Q (IO-Link); 3 x Q (IO-Link)</t>
+          <t>TTL / RS-422; HTL / Push pull; Open Collector; TTL / HTL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MLG-2</t>
+          <t>Industrial Ethernet cables and fieldbus cables</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Giá trị thông số</t>
+          <t>Mô tả ngắn</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -575,19 +575,19 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>MLGxxNxxxxHxxxxx; MLGxxS-xxxxAx; MLGxxN-xxxxEx; MLGxxA-xxxxBx; MLGxxA-xxxxRx; MLGxxA-xxxxIx (+3 tuỳ chọn khác)</t>
+          <t>PROFIBUS, CANopen, Interbus, PROFINET, EtherNet/IP™ &amp; Gigabit Ethernet</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>MLGxxNxxxxHxxxxx; MLGxxS-xxxxAx; MLGxxN-xxxxEx; MLGxxA-xxxxBx; MLGxxA-xxxxRx; MLGxxA-xxxxIx (+3 tuỳ chọn khác)</t>
+          <t>PROFIBUS, CANopen, Interbus, PROFINET, EtherNet/IP™ &amp; Gigabit Ethernet</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MLG-2 WebChecker</t>
+          <t>DWS Dynamic</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -602,19 +602,19 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>4 x Q (IO-Link); 1 x analog + 3 x Q (IO-Link); RS-485 + 2 x Q (IO-Link); 2 x analog + 2 x Q (IO-Link)</t>
+          <t>1D; 2D; RFID; PDF417; Aztec; 4-state; Maxi-Code</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>4 x Q (IO-Link); 1 x analog + 3 x Q (IO-Link); RS-485 + 2 x Q (IO-Link); 2 x analog + 2 x Q (IO-Link)</t>
+          <t>1D; 2D; RFID; PDF417; Aztec; 4-state; Maxi-Code</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>W12</t>
+          <t>DWS Pallet</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -629,39 +629,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>W12-3; W12-2 AS-i; W12 Teflon; W12; W12-2 Laser; W12G</t>
+          <t>1D; 2D; PDF417; Aztec; 4-state; Maxi-Code</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>W12-3; W12-2 AS-i; W12 Teflon; W12; W12-2 Laser; W12G</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Industrial Ethernet cables and fieldbus cables</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Mô tả ngắn</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>chua dich</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>PROFIBUS, CANopen, Interbus, PROFINET, EtherNet/IP™ &amp; Gigabit Ethernet</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>PROFIBUS, CANopen, Interbus, PROFINET, EtherNet/IP™ &amp; Gigabit Ethernet</t>
+          <t>1D; 2D; PDF417; Aztec; 4-state; Maxi-Code</t>
         </is>
       </c>
     </row>

--- a/data/Noi dung SICK/00 CAN SOAT DICH.xlsx
+++ b/data/Noi dung SICK/00 CAN SOAT DICH.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>FlexChain</t>
+          <t>HF transponders</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -494,19 +494,19 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>IO-Link (V1.1); Serial (RS-485); CANopen; IO-Link; Serial</t>
+          <t>NXP ICODE SLIX2; Fujitsu MB89R118; Texas Instruments Tag-it HF-I; NXP ICODE SLIX</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>IO-Link (V1.1); Serial (RS-485); CANopen; IO-Link; Serial</t>
+          <t>NXP ICODE SLIX2; Fujitsu MB89R118; Texas Instruments Tag-it HF-I; NXP ICODE SLIX</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Visionary-B Two</t>
+          <t>UHF transponders</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -521,19 +521,19 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>SICK AppStudio, SICK AppManager, SOPASair</t>
+          <t>NXP UCODE G2iM; Impinj Monza 4E; NXP UCODE 9xm; Impinj Monza 4QT; Impinj Monza X 8k; NXP UCODE G2XM (+9 tuỳ chọn khác)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>SICK AppStudio, SICK AppManager, SOPASair</t>
+          <t>NXP UCODE G2iM; Impinj Monza 4E; NXP UCODE 9xm; Impinj Monza 4QT; Impinj Monza X 8k; NXP UCODE G2XM (+9 tuỳ chọn khác)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>DFS2x</t>
+          <t>CLV69x</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -543,51 +543,51 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>chua dich</t>
+          <t>con nguyen tieng Anh</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>TTL / RS-422; HTL / Push pull; Open Collector; TTL / HTL</t>
+          <t>Ethernet; PROFINET; EtherNet/IP™; Serial; CAN; PROFIBUS DP</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>TTL / RS-422; HTL / Push pull; Open Collector; TTL / HTL</t>
+          <t>Ethernet; PROFINET; EtherNet/IP™; Serial; CAN; PROFIBUS DP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Industrial Ethernet cables and fieldbus cables</t>
+          <t>GLS6</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Mô tả ngắn</t>
+          <t>Giá trị thông số</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>chua dich</t>
+          <t>con nguyen tieng Anh</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>PROFIBUS, CANopen, Interbus, PROFINET, EtherNet/IP™ &amp; Gigabit Ethernet</t>
+          <t>Ethernet; PROFINET; EtherNet/IP™; Serial; CAN; CANopen; USB</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>PROFIBUS, CANopen, Interbus, PROFINET, EtherNet/IP™ &amp; Gigabit Ethernet</t>
+          <t>Ethernet; PROFINET; EtherNet/IP™; Serial; CAN; CANopen; USB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>DWS Dynamic</t>
+          <t>Lector61x</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -597,44 +597,368 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>chua dich</t>
+          <t>con nguyen tieng Anh</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>1D; 2D; RFID; PDF417; Aztec; 4-state; Maxi-Code</t>
+          <t>Ethernet; EtherNet/IP™; EtherCAT®; Serial; CAN; CANopen</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>1D; 2D; RFID; PDF417; Aztec; 4-state; Maxi-Code</t>
+          <t>Ethernet; EtherNet/IP™; EtherCAT®; Serial; CAN; CANopen</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>Lector83x</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị thông số</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>con nguyen tieng Anh</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Ethernet; CAN; Serial; USB; EtherNet/IP™; PROFINET</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Ethernet; CAN; Serial; USB; EtherNet/IP™; PROFINET</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Visionary-B Two</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị thông số</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>chua dich</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>SICK AppStudio, SICK AppManager, SOPASair</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>SICK AppStudio, SICK AppManager, SOPASair</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>RFH6xx</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị thông số</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>con nguyen tieng Anh</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Ethernet; PROFINET; EtherNet/IP™; EtherCAT®; Serial; CAN; CANopen; PROFIBUS DP</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Ethernet; PROFINET; EtherNet/IP™; EtherCAT®; Serial; CAN; CANopen; PROFIBUS DP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>RFU63x</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị thông số</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>con nguyen tieng Anh</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Ethernet; PROFINET; EtherNet/IP™; EtherCAT®; Serial; CAN; PROFIBUS DP; USB; CANopen</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Ethernet; PROFINET; EtherNet/IP™; EtherCAT®; Serial; CAN; PROFIBUS DP; USB; CANopen</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>RFU65x</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị thông số</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>con nguyen tieng Anh</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Ethernet; PROFINET; EtherNet/IP™; EtherCAT®; Serial; CAN; PROFIBUS DP; USB; CANopen</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Ethernet; PROFINET; EtherNet/IP™; EtherCAT®; Serial; CAN; PROFIBUS DP; USB; CANopen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>DFS2x</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị thông số</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>chua dich</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>TTL / RS-422; HTL / Push pull; Open Collector; TTL / HTL</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>TTL / RS-422; HTL / Push pull; Open Collector; TTL / HTL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>SIM2x00</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị thông số</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>chua dich</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>PROFINET; IO-Link; -; Serial; Incremental; USB (+4 tuỳ chọn khác)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>PROFINET; IO-Link; -; Serial; Incremental; USB (+4 tuỳ chọn khác)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>CDM</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị thông số</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>con nguyen tieng Anh</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>PROFIBUS DP; DeviceNet™; Serial; Ethernet; CAN</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>PROFIBUS DP; DeviceNet™; Serial; Ethernet; CAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>CDF</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị thông số</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>con nguyen tieng Anh</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Serial; CAN; EtherCAT®; PROFINET; PROFIBUS DP</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Serial; CAN; EtherCAT®; PROFINET; PROFIBUS DP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Flexi Soft</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị thông số</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>chua dich</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>CANopen, CC-Link, DeviceNet™, EtherNet/IP™, EtherCAT®, Modbus, PROFINET, PROFIBUS DP, EFI-pro, EtherNet/IP™ CIP Safety™, SSI, Incremental, Serial</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>CANopen, CC-Link, DeviceNet™, EtherNet/IP™, EtherCAT®, Modbus, PROFINET, PROFIBUS DP, EFI-pro, EtherNet/IP™ CIP Safety™, SSI, Incremental, Serial</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>DWS Dynamic</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị thông số</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>chua dich</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>1D; 2D; RFID; PDF417; Aztec; 4-state; Maxi-Code</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>1D; 2D; RFID; PDF417; Aztec; 4-state; Maxi-Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
           <t>DWS Pallet</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Giá trị thông số</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị thông số</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>chua dich</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>1D; 2D; PDF417; Aztec; 4-state; Maxi-Code</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>1D; 2D; PDF417; Aztec; 4-state; Maxi-Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>ICR Identification System</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị thông số</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>con nguyen tieng Anh</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Serial; CAN; PROFIBUS DP; Ethernet</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Serial; CAN; PROFIBUS DP; Ethernet</t>
         </is>
       </c>
     </row>
